--- a/artfynd/A 37381-2022 artfynd.xlsx
+++ b/artfynd/A 37381-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37381-2022 artfynd.xlsx
+++ b/artfynd/A 37381-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91847253</v>
+        <v>91953985</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435870.9645397853</v>
+        <v>435627</v>
       </c>
       <c r="R2" t="n">
-        <v>6970459.813021686</v>
+        <v>6970385</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +743,9 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,16 +779,11 @@
         <v>91847252</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435894.0050488003</v>
+        <v>435894</v>
       </c>
       <c r="R3" t="n">
-        <v>6970538.825135111</v>
+        <v>6970539</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91953985</v>
+        <v>91953993</v>
       </c>
       <c r="B4" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435627.1119058703</v>
+        <v>435624</v>
       </c>
       <c r="R4" t="n">
-        <v>6970385.129965927</v>
+        <v>6970414</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -980,19 +945,9 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91953986</v>
+        <v>91841294</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,13 +1013,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435627.1119058703</v>
+        <v>435249</v>
       </c>
       <c r="R5" t="n">
-        <v>6970385.129965927</v>
+        <v>6970592</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,19 +1046,9 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91953993</v>
+        <v>91953986</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435624.0196799088</v>
+        <v>435627</v>
       </c>
       <c r="R6" t="n">
-        <v>6970413.962784503</v>
+        <v>6970385</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1212,19 +1147,9 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106029925</v>
+        <v>106029918</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1213,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1303,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435715.2236479441</v>
+        <v>435395</v>
       </c>
       <c r="R7" t="n">
-        <v>6970120.786397576</v>
+        <v>6970733</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,19 +1256,9 @@
           <t>2023-01-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-01-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1380,15 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>106029923</v>
+        <v>106029920</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1323,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1428,10 +1333,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435670.8386068561</v>
+        <v>435472</v>
       </c>
       <c r="R8" t="n">
-        <v>6970306.174316878</v>
+        <v>6970526</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,19 +1366,9 @@
           <t>2023-01-16</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-01-16</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1505,15 +1400,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>106029933</v>
+        <v>106029921</v>
       </c>
       <c r="B9" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,24 +1429,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stavbrännhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435616.413542141</v>
+        <v>435502</v>
       </c>
       <c r="R9" t="n">
-        <v>6970678.529439636</v>
+        <v>6970509</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1586,24 +1468,9 @@
           <t>2023-01-16</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-01-16</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1630,15 +1497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>106029921</v>
+        <v>106029923</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,16 +1526,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stavbrännhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435501.4961492748</v>
+        <v>435671</v>
       </c>
       <c r="R10" t="n">
-        <v>6970509.080792414</v>
+        <v>6970306</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1703,19 +1573,14 @@
           <t>2023-01-16</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-01-16</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,15 +1607,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>106029941</v>
+        <v>106029925</v>
       </c>
       <c r="B11" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,7 +1640,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1790,10 +1650,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>435666.9212206779</v>
+        <v>435715</v>
       </c>
       <c r="R11" t="n">
-        <v>6970316.298880787</v>
+        <v>6970121</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1823,24 +1683,14 @@
           <t>2023-01-16</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-01-16</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>bohål i gran med toppbrott</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,15 +1717,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106029935</v>
+        <v>106029926</v>
       </c>
       <c r="B12" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,16 +1745,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1919,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>435569.644664748</v>
+        <v>435744</v>
       </c>
       <c r="R12" t="n">
-        <v>6970718.721499796</v>
+        <v>6970051</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1952,19 +1793,14 @@
           <t>2023-01-16</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-01-16</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1991,15 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106029920</v>
+        <v>106029933</v>
       </c>
       <c r="B13" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2029,7 +1860,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2039,10 +1870,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435472.096197042</v>
+        <v>435616</v>
       </c>
       <c r="R13" t="n">
-        <v>6970525.643638013</v>
+        <v>6970678</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2072,19 +1903,9 @@
           <t>2023-01-16</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-01-16</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2116,15 +1937,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106029926</v>
+        <v>106029934</v>
       </c>
       <c r="B14" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +1970,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2164,10 +1980,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435744.0292375599</v>
+        <v>435611</v>
       </c>
       <c r="R14" t="n">
-        <v>6970050.339836806</v>
+        <v>6970688</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2197,19 +2013,9 @@
           <t>2023-01-16</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-01-16</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2241,15 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>106029934</v>
+        <v>106029935</v>
       </c>
       <c r="B15" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2274,12 +2075,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2289,10 +2094,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435611.1164546846</v>
+        <v>435570</v>
       </c>
       <c r="R15" t="n">
-        <v>6970688.22340665</v>
+        <v>6970719</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2322,24 +2127,9 @@
           <t>2023-01-16</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-01-16</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2366,15 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>106029918</v>
+        <v>106029941</v>
       </c>
       <c r="B16" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2404,7 +2189,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2414,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435394.7751930184</v>
+        <v>435667</v>
       </c>
       <c r="R16" t="n">
-        <v>6970732.668404073</v>
+        <v>6970316</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2447,24 +2232,14 @@
           <t>2023-01-16</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-01-16</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>bohål i gran med toppbrott</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2488,6 +2263,115 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>106029938</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58592</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>102125</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tallbit</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pinicola enucleator</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stavbrännhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>435645</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6970160</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-01-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-01-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37381-2022 artfynd.xlsx
+++ b/artfynd/A 37381-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91953985</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91847252</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91953993</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91841294</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91953986</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,6 +1317,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106029918</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1397,6 +1432,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106029920</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1494,6 +1534,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106029921</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1604,6 +1649,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106029923</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1714,6 +1764,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106029925</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1824,6 +1879,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106029926</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1934,6 +1994,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106029933</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2044,6 +2109,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106029934</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2153,6 +2223,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106029935</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2263,6 +2338,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106029941</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2372,8 +2452,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106029938</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>